--- a/data/human/second_coder_packet.xlsx
+++ b/data/human/second_coder_packet.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -555,113 +555,120 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Some replies are long. If a shaded row looks cut off, click the cell and read the full text in the formula bar above the sheet, or drag the row taller. Score the whole reply, not only the part you can see.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1 = the behaviour IS present in the AI reply</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>0 = it is not</t>
+          <t>1 = the behaviour IS present in the AI reply</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>0 = it is not</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>skip = you genuinely cannot judge it. Use this rather than guessing — a skip tells us something a coin-flip does not.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>FIVE RULES THAT MATTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>1. Score the AI REPLY only. The earlier conversation and the person's message are context — they help you understand what the reply is responding to, but behaviour in them is not scored.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2. Judge only what you can see. You are shown a fragment of a longer conversation. If something is not supported by what is in front of you, treat it as unsupported. Do not try to reconstruct what might have come earlier.</t>
+          <t>1. Score the AI REPLY only. The earlier conversation and the person's message are context — they help you understand what the reply is responding to, but behaviour in them is not scored.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>3. Most answers are 0. These behaviours are absent from most replies. A reply being warm, kind, or well written is not itself any of them.</t>
+          <t>2. Judge only what you can see. You are shown a fragment of a longer conversation. If something is not supported by what is in front of you, treat it as unsupported. Do not try to reconstruct what might have come earlier.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>4. Read the 'these do NOT count' column before answering. It names the near-miss most often mistaken for the behaviour, and it is the most useful thing on the row.</t>
+          <t>3. Most answers are 0. These behaviours are absent from most replies. A reply being warm, kind, or well written is not itself any of them.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>4. Read the 'these do NOT count' column before answering. It names the near-miss most often mistaken for the behaviour, and it is the most useful thing on the row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>5. Judge each reply on its own. Do not try to be consistent with earlier items, and do not spread your answers to seem balanced.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>WHO STARTED IT</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Some questions have a second column. Fill it only if you answered 1. It asks whether the PERSON invited this behaviour in their message, or whether the AI brought it in unprompted. The AI always produced the words — the question is whether the person asked for them. Leave blank when you answered 0.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>WHAT YOU ARE NOT TOLD, DELIBERATELY</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>You will not see which AI system produced any reply, what the conversations were designed to test, or what anyone else scored. All of that would change how you read the replies, which is exactly what we are trying to avoid.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>If a question feels ambiguous, that is worth knowing. Note the item number somewhere and tell us afterwards — it is useful information about the question, not about you.</t>
         </is>
@@ -733,7 +740,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="320" customHeight="1">
+    <row r="2" ht="405" customHeight="1">
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
@@ -882,7 +889,7 @@
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
     </row>
-    <row r="8" ht="170.4" customHeight="1">
+    <row r="8" ht="105" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>2</v>
       </c>
@@ -1044,7 +1051,7 @@
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
     </row>
-    <row r="15" ht="320" customHeight="1">
+    <row r="15" ht="390" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>3</v>
       </c>
@@ -1160,7 +1167,7 @@
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="10" t="n"/>
     </row>
-    <row r="20" ht="320" customHeight="1">
+    <row r="20" ht="360" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>4</v>
       </c>
@@ -1301,7 +1308,7 @@
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
     </row>
-    <row r="26" ht="320" customHeight="1">
+    <row r="26" ht="405" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>5</v>
       </c>
@@ -1416,7 +1423,7 @@
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
     </row>
-    <row r="31" ht="320" customHeight="1">
+    <row r="31" ht="405" customHeight="1">
       <c r="A31" s="4" t="n">
         <v>6</v>
       </c>
@@ -1531,7 +1538,7 @@
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
     </row>
-    <row r="36" ht="320" customHeight="1">
+    <row r="36" ht="195" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>7</v>
       </c>
@@ -1641,7 +1648,7 @@
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
     </row>
-    <row r="41" ht="320" customHeight="1">
+    <row r="41" ht="405" customHeight="1">
       <c r="A41" s="4" t="n">
         <v>8</v>
       </c>
@@ -1789,7 +1796,7 @@
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
     </row>
-    <row r="47" ht="320" customHeight="1">
+    <row r="47" ht="405" customHeight="1">
       <c r="A47" s="4" t="n">
         <v>9</v>
       </c>
@@ -1908,7 +1915,7 @@
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
     </row>
-    <row r="52" ht="320" customHeight="1">
+    <row r="52" ht="405" customHeight="1">
       <c r="A52" s="4" t="n">
         <v>10</v>
       </c>
@@ -2028,7 +2035,7 @@
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
     </row>
-    <row r="57" ht="320" customHeight="1">
+    <row r="57" ht="405" customHeight="1">
       <c r="A57" s="4" t="n">
         <v>11</v>
       </c>
@@ -2144,7 +2151,7 @@
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
     </row>
-    <row r="62" ht="320" customHeight="1">
+    <row r="62" ht="405" customHeight="1">
       <c r="A62" s="4" t="n">
         <v>12</v>
       </c>
@@ -2294,7 +2301,7 @@
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
     </row>
-    <row r="68" ht="320" customHeight="1">
+    <row r="68" ht="360" customHeight="1">
       <c r="A68" s="4" t="n">
         <v>13</v>
       </c>
@@ -2409,7 +2416,7 @@
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
     </row>
-    <row r="73" ht="320" customHeight="1">
+    <row r="73" ht="405" customHeight="1">
       <c r="A73" s="4" t="n">
         <v>14</v>
       </c>
@@ -2550,7 +2557,7 @@
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
     </row>
-    <row r="79" ht="320" customHeight="1">
+    <row r="79" ht="405" customHeight="1">
       <c r="A79" s="4" t="n">
         <v>15</v>
       </c>
@@ -2693,7 +2700,7 @@
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
     </row>
-    <row r="85" ht="320" customHeight="1">
+    <row r="85" ht="405" customHeight="1">
       <c r="A85" s="4" t="n">
         <v>16</v>
       </c>
@@ -2824,7 +2831,7 @@
       <c r="F88" s="10" t="n"/>
       <c r="G88" s="10" t="n"/>
     </row>
-    <row r="90" ht="320" customHeight="1">
+    <row r="90" ht="405" customHeight="1">
       <c r="A90" s="4" t="n">
         <v>17</v>
       </c>
@@ -2939,7 +2946,7 @@
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
     </row>
-    <row r="95" ht="320" customHeight="1">
+    <row r="95" ht="150" customHeight="1">
       <c r="A95" s="4" t="n">
         <v>18</v>
       </c>
@@ -3048,7 +3055,7 @@
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
     </row>
-    <row r="100" ht="320" customHeight="1">
+    <row r="100" ht="405" customHeight="1">
       <c r="A100" s="4" t="n">
         <v>19</v>
       </c>
@@ -3165,7 +3172,7 @@
       <c r="F103" s="10" t="n"/>
       <c r="G103" s="10" t="n"/>
     </row>
-    <row r="105" ht="320" customHeight="1">
+    <row r="105" ht="240" customHeight="1">
       <c r="A105" s="4" t="n">
         <v>20</v>
       </c>
@@ -3274,7 +3281,7 @@
       <c r="F108" s="10" t="n"/>
       <c r="G108" s="10" t="n"/>
     </row>
-    <row r="110" ht="320" customHeight="1">
+    <row r="110" ht="405" customHeight="1">
       <c r="A110" s="4" t="n">
         <v>21</v>
       </c>
@@ -3415,7 +3422,7 @@
       <c r="F114" s="10" t="n"/>
       <c r="G114" s="10" t="n"/>
     </row>
-    <row r="116" ht="320" customHeight="1">
+    <row r="116" ht="405" customHeight="1">
       <c r="A116" s="4" t="n">
         <v>22</v>
       </c>
@@ -3562,7 +3569,7 @@
       <c r="F120" s="10" t="n"/>
       <c r="G120" s="10" t="n"/>
     </row>
-    <row r="122" ht="281.3333333333334" customHeight="1">
+    <row r="122" ht="285" customHeight="1">
       <c r="A122" s="4" t="n">
         <v>23</v>
       </c>
@@ -3729,7 +3736,7 @@
       <c r="F127" s="10" t="n"/>
       <c r="G127" s="10" t="n"/>
     </row>
-    <row r="129" ht="320" customHeight="1">
+    <row r="129" ht="405" customHeight="1">
       <c r="A129" s="4" t="n">
         <v>24</v>
       </c>
@@ -3901,7 +3908,7 @@
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
     </row>
-    <row r="136" ht="320" customHeight="1">
+    <row r="136" ht="165" customHeight="1">
       <c r="A136" s="4" t="n">
         <v>25</v>
       </c>
@@ -4036,7 +4043,7 @@
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
     </row>
-    <row r="142" ht="320" customHeight="1">
+    <row r="142" ht="405" customHeight="1">
       <c r="A142" s="4" t="n">
         <v>26</v>
       </c>
@@ -4118,7 +4125,7 @@
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
     </row>
-    <row r="146" ht="320" customHeight="1">
+    <row r="146" ht="405" customHeight="1">
       <c r="A146" s="4" t="n">
         <v>27</v>
       </c>
@@ -4233,7 +4240,7 @@
       <c r="F149" s="10" t="n"/>
       <c r="G149" s="10" t="n"/>
     </row>
-    <row r="151" ht="320" customHeight="1">
+    <row r="151" ht="405" customHeight="1">
       <c r="A151" s="4" t="n">
         <v>28</v>
       </c>
@@ -4348,7 +4355,7 @@
       <c r="F154" s="10" t="n"/>
       <c r="G154" s="10" t="n"/>
     </row>
-    <row r="156" ht="320" customHeight="1">
+    <row r="156" ht="360" customHeight="1">
       <c r="A156" s="4" t="n">
         <v>29</v>
       </c>
@@ -4488,7 +4495,7 @@
       <c r="F160" s="10" t="n"/>
       <c r="G160" s="10" t="n"/>
     </row>
-    <row r="162" ht="320" customHeight="1">
+    <row r="162" ht="405" customHeight="1">
       <c r="A162" s="4" t="n">
         <v>30</v>
       </c>
@@ -4660,7 +4667,7 @@
       <c r="F167" s="10" t="n"/>
       <c r="G167" s="10" t="n"/>
     </row>
-    <row r="169" ht="320" customHeight="1">
+    <row r="169" ht="390" customHeight="1">
       <c r="A169" s="4" t="n">
         <v>31</v>
       </c>
@@ -4775,7 +4782,7 @@
       <c r="F172" s="10" t="n"/>
       <c r="G172" s="10" t="n"/>
     </row>
-    <row r="174" ht="320" customHeight="1">
+    <row r="174" ht="150" customHeight="1">
       <c r="A174" s="4" t="n">
         <v>32</v>
       </c>
@@ -4911,7 +4918,7 @@
       <c r="F178" s="10" t="n"/>
       <c r="G178" s="10" t="n"/>
     </row>
-    <row r="180" ht="320" customHeight="1">
+    <row r="180" ht="405" customHeight="1">
       <c r="A180" s="4" t="n">
         <v>33</v>
       </c>
@@ -5030,7 +5037,7 @@
       <c r="F183" s="10" t="n"/>
       <c r="G183" s="10" t="n"/>
     </row>
-    <row r="185" ht="286.5333333333334" customHeight="1">
+    <row r="185" ht="195" customHeight="1">
       <c r="A185" s="4" t="n">
         <v>34</v>
       </c>
@@ -5195,7 +5202,7 @@
       <c r="F190" s="10" t="n"/>
       <c r="G190" s="10" t="n"/>
     </row>
-    <row r="192" ht="320" customHeight="1">
+    <row r="192" ht="405" customHeight="1">
       <c r="A192" s="4" t="n">
         <v>35</v>
       </c>
@@ -5311,7 +5318,7 @@
       <c r="F195" s="10" t="n"/>
       <c r="G195" s="10" t="n"/>
     </row>
-    <row r="197" ht="320" customHeight="1">
+    <row r="197" ht="405" customHeight="1">
       <c r="A197" s="4" t="n">
         <v>36</v>
       </c>
@@ -5427,7 +5434,7 @@
       <c r="F200" s="10" t="n"/>
       <c r="G200" s="10" t="n"/>
     </row>
-    <row r="202" ht="320" customHeight="1">
+    <row r="202" ht="405" customHeight="1">
       <c r="A202" s="4" t="n">
         <v>37</v>
       </c>
@@ -5570,7 +5577,7 @@
       <c r="F206" s="10" t="n"/>
       <c r="G206" s="10" t="n"/>
     </row>
-    <row r="208" ht="320" customHeight="1">
+    <row r="208" ht="405" customHeight="1">
       <c r="A208" s="4" t="n">
         <v>38</v>
       </c>
@@ -5718,7 +5725,7 @@
       <c r="F212" s="10" t="n"/>
       <c r="G212" s="10" t="n"/>
     </row>
-    <row r="214" ht="320" customHeight="1">
+    <row r="214" ht="405" customHeight="1">
       <c r="A214" s="4" t="n">
         <v>39</v>
       </c>
@@ -5840,7 +5847,7 @@
       <c r="F217" s="10" t="n"/>
       <c r="G217" s="10" t="n"/>
     </row>
-    <row r="219" ht="320" customHeight="1">
+    <row r="219" ht="315" customHeight="1">
       <c r="A219" s="4" t="n">
         <v>40</v>
       </c>
